--- a/applicability_domain.xlsx
+++ b/applicability_domain.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,6 +476,16 @@
           <t>Standard_Deviation</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Distance_Mean</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Distance_Standard_Deviation</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -507,6 +517,12 @@
       <c r="I2" t="n">
         <v>19.01747201529388</v>
       </c>
+      <c r="J2" t="n">
+        <v>16.38917748917749</v>
+      </c>
+      <c r="K2" t="n">
+        <v>14.99552067949014</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -538,6 +554,12 @@
       <c r="I3" t="n">
         <v>8.892668680237772</v>
       </c>
+      <c r="J3" t="n">
+        <v>6.914718614718615</v>
+      </c>
+      <c r="K3" t="n">
+        <v>8.781087005040252</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -569,6 +591,12 @@
       <c r="I4" t="n">
         <v>24.88357777014392</v>
       </c>
+      <c r="J4" t="n">
+        <v>36.05220779220779</v>
+      </c>
+      <c r="K4" t="n">
+        <v>25.6482708778147</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -600,6 +628,12 @@
       <c r="I5" t="n">
         <v>1.174937289846016</v>
       </c>
+      <c r="J5" t="n">
+        <v>1.942970993948112</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1.193810252142678</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -630,6 +664,12 @@
       </c>
       <c r="I6" t="n">
         <v>34.66964525550613</v>
+      </c>
+      <c r="J6" t="n">
+        <v>57.95238095238096</v>
+      </c>
+      <c r="K6" t="n">
+        <v>35.00776847556019</v>
       </c>
     </row>
   </sheetData>
@@ -13829,7 +13869,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13855,20 +13895,25 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Multivariate_Standardization_Reference</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Multivariate_Threshold_Percentile</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Multivariate_Distance_Threshold</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Number_Complete_Cases</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Number_Inside_Combined_Domain</t>
         </is>
@@ -13892,19 +13937,24 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Euclidean distance after z-standardizing the five predictors</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
+          <t>Euclidean distance after z-standardizing the five predictors using complete-case means and population standard deviations (ddof=0)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Complete predictor cases only; identical reference statistics are saved in Predictor_Ranges and reused for new predictions</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
         <v>95</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>3.978065858446787</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>231</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>213</v>
       </c>
     </row>
